--- a/2026/GALERIA/Octubre/GALERIA Octubre.xlsx
+++ b/2026/GALERIA/Octubre/GALERIA Octubre.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F1E4D84-4AA2-4F2A-AE59-9EF8E1E6A6A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54AEBD82-D64C-49C4-8E3F-6FCA18A1A63E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -370,7 +370,7 @@
     <t>A la administracion se le debe en conepto de "deuda vieja" el monto especificado en el cartel de abajo - Por separado se adeudan honorarios del mes 7, 8 y 9 del 2026</t>
   </si>
   <si>
-    <t>UF 13  DEPOSITO $500.000 15/10</t>
+    <t>UF 13  DEPOSITO $500.000 15/10 y transfirio $60.000</t>
   </si>
 </sst>
 </file>
@@ -1234,6 +1234,8 @@
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1288,6 +1290,45 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1306,12 +1347,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1327,41 +1362,6 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1797,49 +1797,49 @@
       <c r="E6" s="21"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="173" t="s">
+      <c r="B8" s="175" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="173"/>
+      <c r="C8" s="175"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="173"/>
-      <c r="C9" s="173"/>
+      <c r="B9" s="175"/>
+      <c r="C9" s="175"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="173"/>
-      <c r="C10" s="173"/>
+      <c r="B10" s="175"/>
+      <c r="C10" s="175"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="181" t="s">
+      <c r="A13" s="183" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="181"/>
-      <c r="C13" s="181"/>
-      <c r="D13" s="181"/>
-      <c r="E13" s="181"/>
+      <c r="B13" s="183"/>
+      <c r="C13" s="183"/>
+      <c r="D13" s="183"/>
+      <c r="E13" s="183"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="181"/>
-      <c r="B14" s="181"/>
-      <c r="C14" s="181"/>
-      <c r="D14" s="181"/>
-      <c r="E14" s="181"/>
+      <c r="A14" s="183"/>
+      <c r="B14" s="183"/>
+      <c r="C14" s="183"/>
+      <c r="D14" s="183"/>
+      <c r="E14" s="183"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="181"/>
-      <c r="B15" s="181"/>
-      <c r="C15" s="181"/>
-      <c r="D15" s="181"/>
-      <c r="E15" s="181"/>
+      <c r="A15" s="183"/>
+      <c r="B15" s="183"/>
+      <c r="C15" s="183"/>
+      <c r="D15" s="183"/>
+      <c r="E15" s="183"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="181"/>
-      <c r="B16" s="181"/>
-      <c r="C16" s="181"/>
-      <c r="D16" s="181"/>
-      <c r="E16" s="181"/>
+      <c r="A16" s="183"/>
+      <c r="B16" s="183"/>
+      <c r="C16" s="183"/>
+      <c r="D16" s="183"/>
+      <c r="E16" s="183"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
@@ -1866,10 +1866,10 @@
       <c r="G21" s="22"/>
     </row>
     <row r="22" spans="1:8" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="174" t="s">
+      <c r="A22" s="176" t="s">
         <v>110</v>
       </c>
-      <c r="B22" s="175"/>
+      <c r="B22" s="177"/>
       <c r="C22" s="5"/>
       <c r="D22" s="171">
         <v>400000</v>
@@ -1881,10 +1881,10 @@
       <c r="H22" s="22"/>
     </row>
     <row r="23" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="174" t="s">
+      <c r="A23" s="176" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="175"/>
+      <c r="B23" s="177"/>
       <c r="C23" s="5"/>
       <c r="D23" s="171"/>
       <c r="E23" s="121"/>
@@ -1913,10 +1913,10 @@
       <c r="E25" s="106"/>
     </row>
     <row r="26" spans="1:8" s="45" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="174" t="s">
+      <c r="A26" s="176" t="s">
         <v>97</v>
       </c>
-      <c r="B26" s="175"/>
+      <c r="B26" s="177"/>
       <c r="C26" s="133"/>
       <c r="D26" s="172">
         <v>149073.01</v>
@@ -1926,10 +1926,10 @@
       </c>
     </row>
     <row r="27" spans="1:8" s="45" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="174" t="s">
+      <c r="A27" s="176" t="s">
         <v>106</v>
       </c>
-      <c r="B27" s="175"/>
+      <c r="B27" s="177"/>
       <c r="C27" s="133"/>
       <c r="D27" s="168">
         <v>0</v>
@@ -2146,22 +2146,22 @@
       <c r="E49" s="117"/>
     </row>
     <row r="50" spans="1:5" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="174"/>
-      <c r="B50" s="175"/>
+      <c r="A50" s="176"/>
+      <c r="B50" s="177"/>
       <c r="C50" s="5"/>
       <c r="D50" s="103"/>
       <c r="E50" s="101"/>
     </row>
     <row r="51" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="174"/>
-      <c r="B51" s="175"/>
+      <c r="A51" s="176"/>
+      <c r="B51" s="177"/>
       <c r="C51" s="5"/>
       <c r="D51" s="103"/>
       <c r="E51" s="101"/>
     </row>
     <row r="52" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="179"/>
-      <c r="B52" s="180"/>
+      <c r="A52" s="181"/>
+      <c r="B52" s="182"/>
       <c r="C52" s="5"/>
       <c r="D52" s="103"/>
       <c r="E52" s="101"/>
@@ -2246,51 +2246,51 @@
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="178" t="s">
+      <c r="A67" s="180" t="s">
         <v>93</v>
       </c>
-      <c r="B67" s="178"/>
-      <c r="C67" s="178"/>
-      <c r="D67" s="178"/>
-      <c r="E67" s="178"/>
+      <c r="B67" s="180"/>
+      <c r="C67" s="180"/>
+      <c r="D67" s="180"/>
+      <c r="E67" s="180"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="178"/>
-      <c r="B68" s="178"/>
-      <c r="C68" s="178"/>
-      <c r="D68" s="178"/>
-      <c r="E68" s="178"/>
+      <c r="A68" s="180"/>
+      <c r="B68" s="180"/>
+      <c r="C68" s="180"/>
+      <c r="D68" s="180"/>
+      <c r="E68" s="180"/>
     </row>
     <row r="69" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="178"/>
-      <c r="B69" s="178"/>
-      <c r="C69" s="178"/>
-      <c r="D69" s="178"/>
-      <c r="E69" s="178"/>
+      <c r="A69" s="180"/>
+      <c r="B69" s="180"/>
+      <c r="C69" s="180"/>
+      <c r="D69" s="180"/>
+      <c r="E69" s="180"/>
     </row>
     <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="182" t="s">
+      <c r="A71" s="184" t="s">
         <v>109</v>
       </c>
-      <c r="B71" s="183"/>
-      <c r="C71" s="183"/>
-      <c r="D71" s="183"/>
-      <c r="E71" s="184"/>
+      <c r="B71" s="185"/>
+      <c r="C71" s="185"/>
+      <c r="D71" s="185"/>
+      <c r="E71" s="186"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="185"/>
-      <c r="B72" s="186"/>
-      <c r="C72" s="186"/>
-      <c r="D72" s="186"/>
-      <c r="E72" s="187"/>
+      <c r="A72" s="187"/>
+      <c r="B72" s="188"/>
+      <c r="C72" s="188"/>
+      <c r="D72" s="188"/>
+      <c r="E72" s="189"/>
     </row>
     <row r="73" spans="1:5" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="188"/>
-      <c r="B73" s="189"/>
-      <c r="C73" s="189"/>
-      <c r="D73" s="189"/>
-      <c r="E73" s="190"/>
+      <c r="A73" s="190"/>
+      <c r="B73" s="191"/>
+      <c r="C73" s="191"/>
+      <c r="D73" s="191"/>
+      <c r="E73" s="192"/>
     </row>
     <row r="74" spans="1:5" s="130" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="163"/>
@@ -2456,16 +2456,16 @@
     <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="94" spans="1:6" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="177" t="s">
+      <c r="A95" s="179" t="s">
         <v>50</v>
       </c>
-      <c r="B95" s="177"/>
-      <c r="C95" s="177"/>
+      <c r="B95" s="179"/>
+      <c r="C95" s="179"/>
     </row>
     <row r="96" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="177"/>
-      <c r="B96" s="177"/>
-      <c r="C96" s="177"/>
+      <c r="A96" s="179"/>
+      <c r="B96" s="179"/>
+      <c r="C96" s="179"/>
     </row>
     <row r="97" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="118"/>
@@ -2488,32 +2488,32 @@
       <c r="M99" s="8"/>
     </row>
     <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="176"/>
-      <c r="B100" s="176"/>
-      <c r="C100" s="176"/>
-      <c r="D100" s="176"/>
-      <c r="E100" s="176"/>
+      <c r="A100" s="178"/>
+      <c r="B100" s="178"/>
+      <c r="C100" s="178"/>
+      <c r="D100" s="178"/>
+      <c r="E100" s="178"/>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A101" s="176"/>
-      <c r="B101" s="176"/>
-      <c r="C101" s="176"/>
-      <c r="D101" s="176"/>
-      <c r="E101" s="176"/>
+      <c r="A101" s="178"/>
+      <c r="B101" s="178"/>
+      <c r="C101" s="178"/>
+      <c r="D101" s="178"/>
+      <c r="E101" s="178"/>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A102" s="176"/>
-      <c r="B102" s="176"/>
-      <c r="C102" s="176"/>
-      <c r="D102" s="176"/>
-      <c r="E102" s="176"/>
+      <c r="A102" s="178"/>
+      <c r="B102" s="178"/>
+      <c r="C102" s="178"/>
+      <c r="D102" s="178"/>
+      <c r="E102" s="178"/>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A103" s="176"/>
-      <c r="B103" s="176"/>
-      <c r="C103" s="176"/>
-      <c r="D103" s="176"/>
-      <c r="E103" s="176"/>
+      <c r="A103" s="178"/>
+      <c r="B103" s="178"/>
+      <c r="C103" s="178"/>
+      <c r="D103" s="178"/>
+      <c r="E103" s="178"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -2564,12 +2564,12 @@
     <row r="1" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
-      <c r="C1" s="191" t="s">
+      <c r="C1" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
@@ -2584,10 +2584,10 @@
     <row r="2" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
-      <c r="C2" s="192"/>
-      <c r="D2" s="192"/>
-      <c r="E2" s="192"/>
-      <c r="F2" s="192"/>
+      <c r="C2" s="207"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="207"/>
+      <c r="F2" s="207"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -2602,10 +2602,10 @@
     <row r="3" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
-      <c r="C3" s="192"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="192"/>
-      <c r="F3" s="192"/>
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -2613,11 +2613,11 @@
         <v>80</v>
       </c>
       <c r="K3" s="6"/>
-      <c r="L3" s="193">
+      <c r="L3" s="208">
         <f>Q3</f>
         <v>1166391.26</v>
       </c>
-      <c r="M3" s="193"/>
+      <c r="M3" s="208"/>
       <c r="N3" s="62"/>
       <c r="O3" s="62"/>
       <c r="P3" s="22"/>
@@ -2628,10 +2628,10 @@
     <row r="4" spans="1:18" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="192"/>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
+      <c r="C4" s="207"/>
+      <c r="D4" s="207"/>
+      <c r="E4" s="207"/>
+      <c r="F4" s="207"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -2639,97 +2639,97 @@
         <v>99</v>
       </c>
       <c r="K4" s="6"/>
-      <c r="L4" s="194"/>
-      <c r="M4" s="194"/>
+      <c r="L4" s="209"/>
+      <c r="M4" s="209"/>
       <c r="N4" s="64"/>
       <c r="O4" s="64"/>
     </row>
     <row r="5" spans="1:18" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="199" t="s">
+      <c r="A5" s="212" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="200"/>
-      <c r="C5" s="200"/>
-      <c r="D5" s="200"/>
-      <c r="E5" s="200"/>
-      <c r="F5" s="200"/>
-      <c r="G5" s="200"/>
-      <c r="H5" s="200"/>
-      <c r="I5" s="200"/>
-      <c r="J5" s="200"/>
-      <c r="K5" s="200"/>
-      <c r="L5" s="200"/>
-      <c r="M5" s="200"/>
-      <c r="N5" s="200"/>
-      <c r="O5" s="201"/>
+      <c r="B5" s="213"/>
+      <c r="C5" s="213"/>
+      <c r="D5" s="213"/>
+      <c r="E5" s="213"/>
+      <c r="F5" s="213"/>
+      <c r="G5" s="213"/>
+      <c r="H5" s="213"/>
+      <c r="I5" s="213"/>
+      <c r="J5" s="213"/>
+      <c r="K5" s="213"/>
+      <c r="L5" s="213"/>
+      <c r="M5" s="213"/>
+      <c r="N5" s="213"/>
+      <c r="O5" s="214"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="195" t="s">
+      <c r="A6" s="210" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="197" t="s">
+      <c r="B6" s="194" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="197" t="s">
+      <c r="C6" s="194" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="197" t="s">
+      <c r="D6" s="194" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="197" t="s">
+      <c r="E6" s="194" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="197" t="s">
+      <c r="F6" s="194" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="197" t="s">
+      <c r="G6" s="194" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="213" t="s">
+      <c r="H6" s="203" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="213" t="s">
+      <c r="I6" s="203" t="s">
         <v>87</v>
       </c>
-      <c r="J6" s="208" t="s">
+      <c r="J6" s="198" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="208" t="s">
+      <c r="K6" s="198" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="211" t="s">
+      <c r="L6" s="201" t="s">
         <v>54</v>
       </c>
       <c r="M6" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="N6" s="206" t="s">
+      <c r="N6" s="196" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="202" t="s">
+      <c r="O6" s="215" t="s">
         <v>52</v>
       </c>
       <c r="R6" s="51"/>
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="196"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
-      <c r="D7" s="205"/>
-      <c r="E7" s="198"/>
-      <c r="F7" s="198"/>
-      <c r="G7" s="198"/>
-      <c r="H7" s="214"/>
-      <c r="I7" s="214"/>
-      <c r="J7" s="209"/>
-      <c r="K7" s="210"/>
-      <c r="L7" s="212"/>
+      <c r="A7" s="211"/>
+      <c r="B7" s="205"/>
+      <c r="C7" s="205"/>
+      <c r="D7" s="195"/>
+      <c r="E7" s="205"/>
+      <c r="F7" s="205"/>
+      <c r="G7" s="205"/>
+      <c r="H7" s="204"/>
+      <c r="I7" s="204"/>
+      <c r="J7" s="199"/>
+      <c r="K7" s="200"/>
+      <c r="L7" s="202"/>
       <c r="M7" s="65" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="N7" s="207"/>
-      <c r="O7" s="203"/>
+      <c r="N7" s="197"/>
+      <c r="O7" s="216"/>
     </row>
     <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
@@ -3417,11 +3417,11 @@
       <c r="A20" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="215">
+      <c r="B20" s="173">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="C20" s="215" t="s">
+      <c r="C20" s="173" t="s">
         <v>70</v>
       </c>
       <c r="D20" s="86"/>
@@ -4276,96 +4276,87 @@
     </row>
     <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="204" t="s">
+      <c r="C38" s="193" t="s">
         <v>91</v>
       </c>
-      <c r="D38" s="204"/>
-      <c r="E38" s="204"/>
-      <c r="F38" s="204"/>
-      <c r="G38" s="204"/>
-      <c r="H38" s="204"/>
-      <c r="I38" s="204"/>
-      <c r="J38" s="204"/>
-      <c r="K38" s="204"/>
-      <c r="L38" s="204"/>
-      <c r="M38" s="204"/>
+      <c r="D38" s="193"/>
+      <c r="E38" s="193"/>
+      <c r="F38" s="193"/>
+      <c r="G38" s="193"/>
+      <c r="H38" s="193"/>
+      <c r="I38" s="193"/>
+      <c r="J38" s="193"/>
+      <c r="K38" s="193"/>
+      <c r="L38" s="193"/>
+      <c r="M38" s="193"/>
     </row>
     <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="204"/>
-      <c r="D39" s="204"/>
-      <c r="E39" s="204"/>
-      <c r="F39" s="204"/>
-      <c r="G39" s="204"/>
-      <c r="H39" s="204"/>
-      <c r="I39" s="204"/>
-      <c r="J39" s="204"/>
-      <c r="K39" s="204"/>
-      <c r="L39" s="204"/>
-      <c r="M39" s="204"/>
+      <c r="C39" s="193"/>
+      <c r="D39" s="193"/>
+      <c r="E39" s="193"/>
+      <c r="F39" s="193"/>
+      <c r="G39" s="193"/>
+      <c r="H39" s="193"/>
+      <c r="I39" s="193"/>
+      <c r="J39" s="193"/>
+      <c r="K39" s="193"/>
+      <c r="L39" s="193"/>
+      <c r="M39" s="193"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="204"/>
-      <c r="D40" s="204"/>
-      <c r="E40" s="204"/>
-      <c r="F40" s="204"/>
-      <c r="G40" s="204"/>
-      <c r="H40" s="204"/>
-      <c r="I40" s="204"/>
-      <c r="J40" s="204"/>
-      <c r="K40" s="204"/>
-      <c r="L40" s="204"/>
-      <c r="M40" s="204"/>
+      <c r="C40" s="193"/>
+      <c r="D40" s="193"/>
+      <c r="E40" s="193"/>
+      <c r="F40" s="193"/>
+      <c r="G40" s="193"/>
+      <c r="H40" s="193"/>
+      <c r="I40" s="193"/>
+      <c r="J40" s="193"/>
+      <c r="K40" s="193"/>
+      <c r="L40" s="193"/>
+      <c r="M40" s="193"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="204"/>
-      <c r="D41" s="204"/>
-      <c r="E41" s="204"/>
-      <c r="F41" s="204"/>
-      <c r="G41" s="204"/>
-      <c r="H41" s="204"/>
-      <c r="I41" s="204"/>
-      <c r="J41" s="204"/>
-      <c r="K41" s="204"/>
-      <c r="L41" s="204"/>
-      <c r="M41" s="204"/>
+      <c r="C41" s="193"/>
+      <c r="D41" s="193"/>
+      <c r="E41" s="193"/>
+      <c r="F41" s="193"/>
+      <c r="G41" s="193"/>
+      <c r="H41" s="193"/>
+      <c r="I41" s="193"/>
+      <c r="J41" s="193"/>
+      <c r="K41" s="193"/>
+      <c r="L41" s="193"/>
+      <c r="M41" s="193"/>
     </row>
     <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="204"/>
-      <c r="D42" s="204"/>
-      <c r="E42" s="204"/>
-      <c r="F42" s="204"/>
-      <c r="G42" s="204"/>
-      <c r="H42" s="204"/>
-      <c r="I42" s="204"/>
-      <c r="J42" s="204"/>
-      <c r="K42" s="204"/>
-      <c r="L42" s="204"/>
-      <c r="M42" s="204"/>
+      <c r="C42" s="193"/>
+      <c r="D42" s="193"/>
+      <c r="E42" s="193"/>
+      <c r="F42" s="193"/>
+      <c r="G42" s="193"/>
+      <c r="H42" s="193"/>
+      <c r="I42" s="193"/>
+      <c r="J42" s="193"/>
+      <c r="K42" s="193"/>
+      <c r="L42" s="193"/>
+      <c r="M42" s="193"/>
     </row>
     <row r="43" spans="1:17" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="204"/>
-      <c r="D43" s="204"/>
-      <c r="E43" s="204"/>
-      <c r="F43" s="204"/>
-      <c r="G43" s="204"/>
-      <c r="H43" s="204"/>
-      <c r="I43" s="204"/>
-      <c r="J43" s="204"/>
-      <c r="K43" s="204"/>
-      <c r="L43" s="204"/>
-      <c r="M43" s="204"/>
+      <c r="C43" s="193"/>
+      <c r="D43" s="193"/>
+      <c r="E43" s="193"/>
+      <c r="F43" s="193"/>
+      <c r="G43" s="193"/>
+      <c r="H43" s="193"/>
+      <c r="I43" s="193"/>
+      <c r="J43" s="193"/>
+      <c r="K43" s="193"/>
+      <c r="L43" s="193"/>
+      <c r="M43" s="193"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C38:M43"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
     <mergeCell ref="C1:F4"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="L4:M4"/>
@@ -4376,6 +4367,15 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="A5:O5"/>
     <mergeCell ref="O6:O7"/>
+    <mergeCell ref="C38:M43"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4388,7 +4388,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="216" t="s">
+      <c r="B4" s="174" t="s">
         <v>112</v>
       </c>
     </row>
